--- a/EntrySurvey_JaydenUpdated.xlsx
+++ b/EntrySurvey_JaydenUpdated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phamn\Documents\Project\Rebound Classes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92688E31-092F-480A-ABDB-32F88F7BA864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C8EC584-EE8E-4328-9E58-EB89736FD4D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{B19B9D2F-956D-BE40-A123-87133FD4CF0A}"/>
   </bookViews>

--- a/EntrySurvey_JaydenUpdated.xlsx
+++ b/EntrySurvey_JaydenUpdated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phamn\Documents\Project\Rebound Classes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C8EC584-EE8E-4328-9E58-EB89736FD4D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED40BBA5-E710-4B8F-B652-056D901312D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{B19B9D2F-956D-BE40-A123-87133FD4CF0A}"/>
   </bookViews>
@@ -1784,9 +1784,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4453E47D-C568-EE4F-A623-6435D780369E}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AB94"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="2" width="15.58203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.9140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="409.5" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
@@ -1874,7 +1877,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" hidden="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
         <v>45712.412314814814</v>
       </c>
@@ -1915,7 +1918,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:28" hidden="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>45714.877303240741</v>
       </c>
@@ -1959,7 +1962,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:28" hidden="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>45715.021354166667</v>
       </c>
@@ -2637,7 +2640,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:28" hidden="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>45725.762175925927</v>
       </c>
@@ -3866,7 +3869,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:28" hidden="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <v>45729.047708333332</v>
       </c>
@@ -3937,7 +3940,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="30" spans="1:28" hidden="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <v>45732.318287037036</v>
       </c>
@@ -4778,7 +4781,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:28" hidden="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A41" s="2">
         <v>45736.891817129632</v>
       </c>
@@ -5385,7 +5388,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="1:28" hidden="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A49" s="2">
         <v>45750.059432870374</v>
       </c>
@@ -5995,7 +5998,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="57" spans="1:28" hidden="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A57" s="2">
         <v>45785.086319444446</v>
       </c>
@@ -6119,7 +6122,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="59" spans="1:28" hidden="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A59" s="2">
         <v>45799.018425925926</v>
       </c>
@@ -6163,7 +6166,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="60" spans="1:28" hidden="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A60" s="2">
         <v>45802.902407407404</v>
       </c>
@@ -6592,7 +6595,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="66" spans="1:28" hidden="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A66" s="2">
         <v>45862.239618055559</v>
       </c>
@@ -7116,7 +7119,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="73" spans="1:28" hidden="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A73" s="2">
         <v>45873.040925925925</v>
       </c>
@@ -7658,7 +7661,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="80" spans="1:28" hidden="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A80" s="2">
         <v>45878.412210648145</v>
       </c>
@@ -7702,7 +7705,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="81" spans="1:28" hidden="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A81" s="2">
         <v>45882.166655092595</v>
       </c>
@@ -7847,7 +7850,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="83" spans="1:28" hidden="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A83" s="2">
         <v>45883.868055555555</v>
       </c>
@@ -8291,7 +8294,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="89" spans="1:28" hidden="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A89" s="2">
         <v>45890.859143518515</v>
       </c>
@@ -8335,7 +8338,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="90" spans="1:28" hidden="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A90" s="2">
         <v>45891.38009259259</v>
       </c>
@@ -8409,7 +8412,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="91" spans="1:28" hidden="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A91" s="2">
         <v>45893.277256944442</v>
       </c>
@@ -8703,13 +8706,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB94" xr:uid="{4453E47D-C568-EE4F-A623-6435D780369E}">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="TRUE"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>